--- a/CRUDEX/Assets/CRUDEx_DataTypes_All_DBMS.xlsx
+++ b/CRUDEX/Assets/CRUDEx_DataTypes_All_DBMS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CRUDEX-C#\SGSI_CRUDEX\CRUDEX\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD9CB6E-9D4A-4DBE-89A0-4C7100FC3F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD735B8-3872-4F2D-A79D-66D4A21710F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="281">
   <si>
     <t>DBMS</t>
   </si>
@@ -732,6 +732,150 @@
   </si>
   <si>
     <t>16-bit integer</t>
+  </si>
+  <si>
+    <t>Informix</t>
+  </si>
+  <si>
+    <t>SERIAL</t>
+  </si>
+  <si>
+    <t>Auto-increment 32-bit integer</t>
+  </si>
+  <si>
+    <t>SERIAL8</t>
+  </si>
+  <si>
+    <t>Auto-increment 64-bit integer</t>
+  </si>
+  <si>
+    <t>INT8</t>
+  </si>
+  <si>
+    <t>Exact 64-bit integer (non-autoincrement)</t>
+  </si>
+  <si>
+    <t>Exact numeric; synonym: NUMERIC</t>
+  </si>
+  <si>
+    <t>Exact numeric; synonym: DECIMAL</t>
+  </si>
+  <si>
+    <t>MONEY(p,s)</t>
+  </si>
+  <si>
+    <t>Exact fixed-point currency</t>
+  </si>
+  <si>
+    <t>Approximate floating point (precision depends on p)</t>
+  </si>
+  <si>
+    <t>SMALLFLOAT</t>
+  </si>
+  <si>
+    <t>Approximate floating point; synonym of SMALLFLOAT</t>
+  </si>
+  <si>
+    <t>Highly flexible; supports qualifiers (YEAR TO FRACTION(n))</t>
+  </si>
+  <si>
+    <t>INTERVAL</t>
+  </si>
+  <si>
+    <t>Stores a duration; supports qualifiers (DAY TO SECOND, etc.)</t>
+  </si>
+  <si>
+    <t>Fixed-length Unicode character string (UTF-8/UTF-16 depends on locale)</t>
+  </si>
+  <si>
+    <t>Character large object (CLOB)</t>
+  </si>
+  <si>
+    <t>BYTE</t>
+  </si>
+  <si>
+    <t>Binary large object (BLOB)</t>
+  </si>
+  <si>
+    <t>Stores TRUE or FALSE (introduced in 12.10+)</t>
+  </si>
+  <si>
+    <t>Unique identifier of row within table</t>
+  </si>
+  <si>
+    <t>BIGSERIAL</t>
+  </si>
+  <si>
+    <t>Alias of SERIAL8</t>
+  </si>
+  <si>
+    <t>LVARCHAR(n)</t>
+  </si>
+  <si>
+    <t>Lightweight VARCHAR up to 32 KB</t>
+  </si>
+  <si>
+    <t>Character large object, synonym of TEXT</t>
+  </si>
+  <si>
+    <t>Binary large object, synonym of BYTE</t>
+  </si>
+  <si>
+    <t>Native JSON data type (stored as BSON internally)</t>
+  </si>
+  <si>
+    <t>BSON</t>
+  </si>
+  <si>
+    <t>Binary JSON structure type; used by JSON columns internally</t>
+  </si>
+  <si>
+    <t>XML data type (stored as CLOB with validation)</t>
+  </si>
+  <si>
+    <t>IDSSECURITYLABEL</t>
+  </si>
+  <si>
+    <t>Used for label-based access control</t>
+  </si>
+  <si>
+    <t>ROW</t>
+  </si>
+  <si>
+    <t>Composite row type (similar to record/struct)</t>
+  </si>
+  <si>
+    <t>LIST</t>
+  </si>
+  <si>
+    <t>Ordered collection type</t>
+  </si>
+  <si>
+    <t>Unordered collection type (unique elements)</t>
+  </si>
+  <si>
+    <t>MULTISET</t>
+  </si>
+  <si>
+    <t>Unordered collection type (duplicates allowed)</t>
+  </si>
+  <si>
+    <t>DISTINCT</t>
+  </si>
+  <si>
+    <t>User-defined type based on existing type</t>
+  </si>
+  <si>
+    <t>UDT</t>
+  </si>
+  <si>
+    <t>User-defined type (opaque)</t>
+  </si>
+  <si>
+    <t>JSONBSON</t>
+  </si>
+  <si>
+    <t>Used internally for JSON/BSON hybrid storage</t>
   </si>
 </sst>
 </file>
@@ -1094,13 +1238,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D273"/>
+  <dimension ref="A1:D312"/>
   <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="55.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="60.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -4454,6 +4598,552 @@
         <v>189</v>
       </c>
     </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
+        <v>233</v>
+      </c>
+      <c r="B274" t="s">
+        <v>58</v>
+      </c>
+      <c r="C274" t="s">
+        <v>81</v>
+      </c>
+      <c r="D274" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
+        <v>233</v>
+      </c>
+      <c r="B275" t="s">
+        <v>58</v>
+      </c>
+      <c r="C275" t="s">
+        <v>82</v>
+      </c>
+      <c r="D275" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A276" t="s">
+        <v>233</v>
+      </c>
+      <c r="B276" t="s">
+        <v>58</v>
+      </c>
+      <c r="C276" t="s">
+        <v>83</v>
+      </c>
+      <c r="D276" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A277" t="s">
+        <v>233</v>
+      </c>
+      <c r="B277" t="s">
+        <v>58</v>
+      </c>
+      <c r="C277" t="s">
+        <v>234</v>
+      </c>
+      <c r="D277" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A278" t="s">
+        <v>233</v>
+      </c>
+      <c r="B278" t="s">
+        <v>58</v>
+      </c>
+      <c r="C278" t="s">
+        <v>236</v>
+      </c>
+      <c r="D278" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A279" t="s">
+        <v>233</v>
+      </c>
+      <c r="B279" t="s">
+        <v>58</v>
+      </c>
+      <c r="C279" t="s">
+        <v>238</v>
+      </c>
+      <c r="D279" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A280" t="s">
+        <v>233</v>
+      </c>
+      <c r="B280" t="s">
+        <v>58</v>
+      </c>
+      <c r="C280" t="s">
+        <v>229</v>
+      </c>
+      <c r="D280" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A281" t="s">
+        <v>233</v>
+      </c>
+      <c r="B281" t="s">
+        <v>58</v>
+      </c>
+      <c r="C281" t="s">
+        <v>227</v>
+      </c>
+      <c r="D281" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A282" t="s">
+        <v>233</v>
+      </c>
+      <c r="B282" t="s">
+        <v>58</v>
+      </c>
+      <c r="C282" t="s">
+        <v>242</v>
+      </c>
+      <c r="D282" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A283" t="s">
+        <v>233</v>
+      </c>
+      <c r="B283" t="s">
+        <v>58</v>
+      </c>
+      <c r="C283" t="s">
+        <v>224</v>
+      </c>
+      <c r="D283" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A284" t="s">
+        <v>233</v>
+      </c>
+      <c r="B284" t="s">
+        <v>58</v>
+      </c>
+      <c r="C284" t="s">
+        <v>245</v>
+      </c>
+      <c r="D284" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A285" t="s">
+        <v>233</v>
+      </c>
+      <c r="B285" t="s">
+        <v>58</v>
+      </c>
+      <c r="C285" t="s">
+        <v>87</v>
+      </c>
+      <c r="D285" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A286" t="s">
+        <v>233</v>
+      </c>
+      <c r="B286" t="s">
+        <v>58</v>
+      </c>
+      <c r="C286" t="s">
+        <v>183</v>
+      </c>
+      <c r="D286" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A287" t="s">
+        <v>233</v>
+      </c>
+      <c r="B287" t="s">
+        <v>18</v>
+      </c>
+      <c r="C287" t="s">
+        <v>62</v>
+      </c>
+      <c r="D287" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A288" t="s">
+        <v>233</v>
+      </c>
+      <c r="B288" t="s">
+        <v>18</v>
+      </c>
+      <c r="C288" t="s">
+        <v>107</v>
+      </c>
+      <c r="D288" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A289" t="s">
+        <v>233</v>
+      </c>
+      <c r="B289" t="s">
+        <v>18</v>
+      </c>
+      <c r="C289" t="s">
+        <v>248</v>
+      </c>
+      <c r="D289" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A290" t="s">
+        <v>233</v>
+      </c>
+      <c r="B290" t="s">
+        <v>49</v>
+      </c>
+      <c r="C290" t="s">
+        <v>217</v>
+      </c>
+      <c r="D290" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A291" t="s">
+        <v>233</v>
+      </c>
+      <c r="B291" t="s">
+        <v>49</v>
+      </c>
+      <c r="C291" t="s">
+        <v>215</v>
+      </c>
+      <c r="D291" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A292" t="s">
+        <v>233</v>
+      </c>
+      <c r="B292" t="s">
+        <v>49</v>
+      </c>
+      <c r="C292" t="s">
+        <v>211</v>
+      </c>
+      <c r="D292" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A293" t="s">
+        <v>233</v>
+      </c>
+      <c r="B293" t="s">
+        <v>49</v>
+      </c>
+      <c r="C293" t="s">
+        <v>209</v>
+      </c>
+      <c r="D293" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A294" t="s">
+        <v>233</v>
+      </c>
+      <c r="B294" t="s">
+        <v>49</v>
+      </c>
+      <c r="C294" t="s">
+        <v>114</v>
+      </c>
+      <c r="D294" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A295" t="s">
+        <v>233</v>
+      </c>
+      <c r="B295" t="s">
+        <v>33</v>
+      </c>
+      <c r="C295" t="s">
+        <v>252</v>
+      </c>
+      <c r="D295" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A296" t="s">
+        <v>233</v>
+      </c>
+      <c r="B296" t="s">
+        <v>137</v>
+      </c>
+      <c r="C296" t="s">
+        <v>98</v>
+      </c>
+      <c r="D296" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A297" t="s">
+        <v>233</v>
+      </c>
+      <c r="B297" t="s">
+        <v>39</v>
+      </c>
+      <c r="C297" t="s">
+        <v>75</v>
+      </c>
+      <c r="D297" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A298" t="s">
+        <v>233</v>
+      </c>
+      <c r="B298" t="s">
+        <v>39</v>
+      </c>
+      <c r="C298" t="s">
+        <v>256</v>
+      </c>
+      <c r="D298" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A299" t="s">
+        <v>233</v>
+      </c>
+      <c r="B299" t="s">
+        <v>39</v>
+      </c>
+      <c r="C299" t="s">
+        <v>258</v>
+      </c>
+      <c r="D299" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A300" t="s">
+        <v>233</v>
+      </c>
+      <c r="B300" t="s">
+        <v>39</v>
+      </c>
+      <c r="C300" t="s">
+        <v>55</v>
+      </c>
+      <c r="D300" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A301" t="s">
+        <v>233</v>
+      </c>
+      <c r="B301" t="s">
+        <v>39</v>
+      </c>
+      <c r="C301" t="s">
+        <v>72</v>
+      </c>
+      <c r="D301" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A302" t="s">
+        <v>233</v>
+      </c>
+      <c r="B302" t="s">
+        <v>39</v>
+      </c>
+      <c r="C302" t="s">
+        <v>79</v>
+      </c>
+      <c r="D302" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A303" t="s">
+        <v>233</v>
+      </c>
+      <c r="B303" t="s">
+        <v>39</v>
+      </c>
+      <c r="C303" t="s">
+        <v>263</v>
+      </c>
+      <c r="D303" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A304" t="s">
+        <v>233</v>
+      </c>
+      <c r="B304" t="s">
+        <v>39</v>
+      </c>
+      <c r="C304" t="s">
+        <v>97</v>
+      </c>
+      <c r="D304" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A305" t="s">
+        <v>233</v>
+      </c>
+      <c r="B305" t="s">
+        <v>39</v>
+      </c>
+      <c r="C305" t="s">
+        <v>266</v>
+      </c>
+      <c r="D305" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A306" t="s">
+        <v>233</v>
+      </c>
+      <c r="B306" t="s">
+        <v>39</v>
+      </c>
+      <c r="C306" t="s">
+        <v>268</v>
+      </c>
+      <c r="D306" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A307" t="s">
+        <v>233</v>
+      </c>
+      <c r="B307" t="s">
+        <v>39</v>
+      </c>
+      <c r="C307" t="s">
+        <v>270</v>
+      </c>
+      <c r="D307" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A308" t="s">
+        <v>233</v>
+      </c>
+      <c r="B308" t="s">
+        <v>39</v>
+      </c>
+      <c r="C308" t="s">
+        <v>118</v>
+      </c>
+      <c r="D308" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A309" t="s">
+        <v>233</v>
+      </c>
+      <c r="B309" t="s">
+        <v>39</v>
+      </c>
+      <c r="C309" t="s">
+        <v>273</v>
+      </c>
+      <c r="D309" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A310" t="s">
+        <v>233</v>
+      </c>
+      <c r="B310" t="s">
+        <v>39</v>
+      </c>
+      <c r="C310" t="s">
+        <v>275</v>
+      </c>
+      <c r="D310" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A311" t="s">
+        <v>233</v>
+      </c>
+      <c r="B311" t="s">
+        <v>39</v>
+      </c>
+      <c r="C311" t="s">
+        <v>277</v>
+      </c>
+      <c r="D311" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A312" t="s">
+        <v>233</v>
+      </c>
+      <c r="B312" t="s">
+        <v>39</v>
+      </c>
+      <c r="C312" t="s">
+        <v>279</v>
+      </c>
+      <c r="D312" t="s">
+        <v>280</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
